--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -84,12 +84,12 @@
     <t xml:space="preserve">Pemuco</t>
   </si>
   <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -541,7 +541,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>163.92</v>
+        <v>176.17</v>
       </c>
     </row>
     <row r="3">
@@ -558,7 +558,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>151.54</v>
+        <v>163.31</v>
       </c>
     </row>
     <row r="4">
@@ -575,7 +575,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>146.39</v>
+        <v>159.05</v>
       </c>
     </row>
     <row r="5">
@@ -592,7 +592,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>145.84</v>
+        <v>155.59</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>136.05</v>
+        <v>147.03</v>
       </c>
     </row>
     <row r="7">
@@ -626,7 +626,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>134.94</v>
+        <v>144.84</v>
       </c>
     </row>
     <row r="8">
@@ -643,7 +643,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>129.61</v>
+        <v>138.48</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.88</v>
+        <v>125.34</v>
       </c>
     </row>
     <row r="10">
@@ -677,7 +677,7 @@
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.26</v>
+        <v>125.26</v>
       </c>
     </row>
     <row r="11">
@@ -694,7 +694,7 @@
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>112.98</v>
+        <v>120.7</v>
       </c>
     </row>
     <row r="12">
@@ -711,7 +711,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>111.4</v>
+        <v>120.54</v>
       </c>
     </row>
     <row r="13">
@@ -728,7 +728,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>109.96</v>
+        <v>117.82</v>
       </c>
     </row>
     <row r="14">
@@ -745,7 +745,7 @@
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>106.26</v>
+        <v>114.6</v>
       </c>
     </row>
     <row r="15">
@@ -762,7 +762,7 @@
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>105.72</v>
+        <v>113.32</v>
       </c>
     </row>
     <row r="16">
@@ -779,7 +779,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>101.54</v>
+        <v>109.28</v>
       </c>
     </row>
     <row r="17">
@@ -796,7 +796,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>100.17</v>
+        <v>108.28</v>
       </c>
     </row>
     <row r="18">
@@ -807,13 +807,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16102</v>
+        <v>16109</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.98</v>
+        <v>107.91</v>
       </c>
     </row>
     <row r="19">
@@ -824,13 +824,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>16109</v>
+        <v>16102</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>99.87</v>
+        <v>107.21</v>
       </c>
     </row>
     <row r="20">
@@ -847,7 +847,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>88.48</v>
+        <v>94.91</v>
       </c>
     </row>
     <row r="21">
@@ -864,7 +864,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>76.65</v>
+        <v>82.1</v>
       </c>
     </row>
     <row r="22">
@@ -881,7 +881,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>64.67</v>
+        <v>69.23</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Treguaco</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:46</t>
+    <t xml:space="preserve">2026-10-04 10:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:38</t>
+    <t xml:space="preserve">2026-10-05 16:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
